--- a/reports/model_output.xlsx
+++ b/reports/model_output.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly_RawParsed" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Features" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast_Monthly" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast_Annual" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annual_Backtest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection_12M_Rolling" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast_Monthly" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast_Annual" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17525,7 +17526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17569,6 +17570,16 @@
           <t>forecast_total_bn_twd</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>is_complete_12m</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>selection_eligible</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -17576,26 +17587,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SeasonalNaive</t>
+          <t>HW_Damped_Add</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>15.59945123096836</v>
+        <v>18.34470534065316</v>
       </c>
       <c r="E2" t="n">
-        <v>15.88110830194852</v>
+        <v>18.70367391440526</v>
       </c>
       <c r="F2" t="n">
-        <v>-14.62288613039187</v>
+        <v>-18.70367391440525</v>
       </c>
       <c r="G2" t="n">
         <v>21.132039</v>
       </c>
       <c r="H2" t="n">
-        <v>18.041925</v>
+        <v>17.17957133397505</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -17604,115 +17621,139 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HW_Damped</t>
+          <t>SeasonalNaive</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>18.73172099056072</v>
+        <v>15.59945123096836</v>
       </c>
       <c r="E3" t="n">
-        <v>19.05454128669912</v>
+        <v>15.88110830194852</v>
       </c>
       <c r="F3" t="n">
-        <v>-19.05454128669913</v>
+        <v>-14.62288613039187</v>
       </c>
       <c r="G3" t="n">
         <v>21.132039</v>
       </c>
       <c r="H3" t="n">
-        <v>17.10542590402364</v>
+        <v>18.041925</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>HW_Damped_Add</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>10.79458183261901</v>
+        <v>22.48384557168044</v>
       </c>
       <c r="E4" t="n">
-        <v>11.0925492772236</v>
+        <v>21.60758103734666</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.0925492772236</v>
+        <v>21.60758103734666</v>
       </c>
       <c r="G4" t="n">
-        <v>21.132039</v>
+        <v>18.472128</v>
       </c>
       <c r="H4" t="n">
-        <v>18.78795716064289</v>
+        <v>22.4635080269224</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>SeasonalNaive</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>15.36474700252504</v>
+        <v>18.65439035698309</v>
       </c>
       <c r="E5" t="n">
-        <v>15.82449500370378</v>
+        <v>17.97718703551643</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.82449500370377</v>
+        <v>14.39959164423285</v>
       </c>
       <c r="G5" t="n">
+        <v>18.472128</v>
+      </c>
+      <c r="H5" t="n">
         <v>21.132039</v>
       </c>
-      <c r="H5" t="n">
-        <v>17.78800054426427</v>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>HW_Damped_Add</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>15.55985381991653</v>
+        <v>10.40128762984633</v>
       </c>
       <c r="E6" t="n">
-        <v>15.97500968830232</v>
+        <v>10.03101998079455</v>
       </c>
       <c r="F6" t="n">
-        <v>-15.97500968830232</v>
+        <v>2.525909643410142</v>
       </c>
       <c r="G6" t="n">
-        <v>21.132039</v>
+        <v>16.002042</v>
       </c>
       <c r="H6" t="n">
-        <v>17.75619372241417</v>
+        <v>16.40623912202054</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -17723,691 +17764,229 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>18.65439035698309</v>
+        <v>20.4450576597624</v>
       </c>
       <c r="E7" t="n">
-        <v>17.97718703551643</v>
+        <v>18.93917038837919</v>
       </c>
       <c r="F7" t="n">
-        <v>14.39959164423285</v>
+        <v>15.43606747188892</v>
       </c>
       <c r="G7" t="n">
+        <v>16.002042</v>
+      </c>
+      <c r="H7" t="n">
         <v>18.472128</v>
       </c>
-      <c r="H7" t="n">
-        <v>21.132039</v>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HW_Damped</t>
+          <t>HW_Damped_Add</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>23.1441169102926</v>
+        <v>22.718659662082</v>
       </c>
       <c r="E8" t="n">
-        <v>22.36041326262715</v>
+        <v>24.20474832923641</v>
       </c>
       <c r="F8" t="n">
-        <v>22.36041326262713</v>
+        <v>-23.27878541238041</v>
       </c>
       <c r="G8" t="n">
-        <v>18.472128</v>
+        <v>23.070211</v>
       </c>
       <c r="H8" t="n">
-        <v>22.60257215920146</v>
+        <v>17.69974608712662</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>SeasonalNaive</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>20.69301522011358</v>
+        <v>30.15069438637898</v>
       </c>
       <c r="E9" t="n">
-        <v>19.91280476061695</v>
+        <v>31.23982264401483</v>
       </c>
       <c r="F9" t="n">
-        <v>19.83254382698527</v>
+        <v>-30.63764349619516</v>
       </c>
       <c r="G9" t="n">
-        <v>18.472128</v>
+        <v>23.070211</v>
       </c>
       <c r="H9" t="n">
-        <v>22.13562088137682</v>
+        <v>16.002042</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>HW_Damped_Add</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>15.36106498342233</v>
+        <v>16.78642368321008</v>
       </c>
       <c r="E10" t="n">
-        <v>14.7048214820273</v>
+        <v>18.46791036834922</v>
       </c>
       <c r="F10" t="n">
-        <v>14.67932738906065</v>
+        <v>-18.32289790265684</v>
       </c>
       <c r="G10" t="n">
-        <v>18.472128</v>
+        <v>30.344327</v>
       </c>
       <c r="H10" t="n">
-        <v>21.18371214484634</v>
+        <v>24.78436694454167</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SeasonalNaive</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>17.59364657605738</v>
+        <v>23.59741647103776</v>
       </c>
       <c r="E11" t="n">
-        <v>16.80036519556015</v>
+        <v>23.97191409122371</v>
       </c>
       <c r="F11" t="n">
-        <v>16.12231938941353</v>
+        <v>-23.97191409122371</v>
       </c>
       <c r="G11" t="n">
-        <v>18.472128</v>
+        <v>30.344327</v>
       </c>
       <c r="H11" t="n">
-        <v>21.45026347418129</v>
+        <v>23.070211</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SeasonalNaive</t>
+          <t>HW_Damped_Add</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>20.4450576597624</v>
+        <v>24.03899662909659</v>
       </c>
       <c r="E12" t="n">
-        <v>18.93917038837919</v>
+        <v>26.39790876978016</v>
       </c>
       <c r="F12" t="n">
-        <v>15.43606747188892</v>
+        <v>-24.41170991884603</v>
       </c>
       <c r="G12" t="n">
-        <v>16.002042</v>
+        <v>42.30381399999999</v>
       </c>
       <c r="H12" t="n">
-        <v>18.472128</v>
+        <v>31.97672964171182</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HW_Damped</t>
+          <t>SeasonalNaive</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>10.54228352922363</v>
+        <v>47.67483140166131</v>
       </c>
       <c r="E13" t="n">
-        <v>10.18122136235959</v>
+        <v>49.84978186600387</v>
       </c>
       <c r="F13" t="n">
-        <v>2.390138903901873</v>
+        <v>-49.84978186600384</v>
       </c>
       <c r="G13" t="n">
-        <v>16.002042</v>
+        <v>42.30381399999999</v>
       </c>
       <c r="H13" t="n">
-        <v>16.38451303126072</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" t="n">
-        <v>29.39430123209818</v>
-      </c>
-      <c r="E14" t="n">
-        <v>28.9333455645774</v>
-      </c>
-      <c r="F14" t="n">
-        <v>28.93334556457743</v>
-      </c>
-      <c r="G14" t="n">
-        <v>16.002042</v>
-      </c>
-      <c r="H14" t="n">
-        <v>20.63196810924882</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" t="n">
-        <v>14.50438792244816</v>
-      </c>
-      <c r="E15" t="n">
-        <v>13.58558908335442</v>
-      </c>
-      <c r="F15" t="n">
-        <v>12.46081957328408</v>
-      </c>
-      <c r="G15" t="n">
-        <v>16.002042</v>
-      </c>
-      <c r="H15" t="n">
-        <v>17.99602758166114</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.97286945976345</v>
-      </c>
-      <c r="E16" t="n">
-        <v>14.02072720535332</v>
-      </c>
-      <c r="F16" t="n">
-        <v>13.01593097578235</v>
-      </c>
-      <c r="G16" t="n">
-        <v>16.002042</v>
-      </c>
-      <c r="H16" t="n">
-        <v>18.0848567414357</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SeasonalNaive</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D17" t="n">
-        <v>30.15069438637898</v>
-      </c>
-      <c r="E17" t="n">
-        <v>31.23982264401483</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-30.63764349619516</v>
-      </c>
-      <c r="G17" t="n">
-        <v>23.070211</v>
-      </c>
-      <c r="H17" t="n">
-        <v>16.002042</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>12</v>
-      </c>
-      <c r="D18" t="n">
-        <v>22.58208190006742</v>
-      </c>
-      <c r="E18" t="n">
-        <v>24.13234010088585</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-23.39484936186131</v>
-      </c>
-      <c r="G18" t="n">
-        <v>23.070211</v>
-      </c>
-      <c r="H18" t="n">
-        <v>17.67296988908644</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>12</v>
-      </c>
-      <c r="D19" t="n">
-        <v>20.02541955152969</v>
-      </c>
-      <c r="E19" t="n">
-        <v>20.36450344722937</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-17.30030959512665</v>
-      </c>
-      <c r="G19" t="n">
-        <v>23.070211</v>
-      </c>
-      <c r="H19" t="n">
-        <v>19.07899307275104</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>12</v>
-      </c>
-      <c r="D20" t="n">
-        <v>22.68586044686468</v>
-      </c>
-      <c r="E20" t="n">
-        <v>23.51777254633411</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-20.72088792679291</v>
-      </c>
-      <c r="G20" t="n">
-        <v>23.070211</v>
-      </c>
-      <c r="H20" t="n">
-        <v>18.28985843421535</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" t="n">
-        <v>24.41758494949779</v>
-      </c>
-      <c r="E21" t="n">
-        <v>25.54133026800367</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-23.14452625268463</v>
-      </c>
-      <c r="G21" t="n">
-        <v>23.070211</v>
-      </c>
-      <c r="H21" t="n">
-        <v>17.73071995855526</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SeasonalNaive</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>12</v>
-      </c>
-      <c r="D22" t="n">
-        <v>23.59741647103776</v>
-      </c>
-      <c r="E22" t="n">
-        <v>23.97191409122371</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-23.97191409122371</v>
-      </c>
-      <c r="G22" t="n">
-        <v>30.344327</v>
-      </c>
-      <c r="H22" t="n">
-        <v>23.070211</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>12</v>
-      </c>
-      <c r="D23" t="n">
-        <v>16.67404099631285</v>
-      </c>
-      <c r="E23" t="n">
-        <v>18.26679457058207</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-17.91300330918168</v>
-      </c>
-      <c r="G23" t="n">
-        <v>30.344327</v>
-      </c>
-      <c r="H23" t="n">
-        <v>24.90874670034109</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>12</v>
-      </c>
-      <c r="D24" t="n">
-        <v>22.85549795477947</v>
-      </c>
-      <c r="E24" t="n">
-        <v>25.1313771777209</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-25.13137717772089</v>
-      </c>
-      <c r="G24" t="n">
-        <v>30.344327</v>
-      </c>
-      <c r="H24" t="n">
-        <v>22.718379729589</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>12</v>
-      </c>
-      <c r="D25" t="n">
-        <v>21.20591039540898</v>
-      </c>
-      <c r="E25" t="n">
-        <v>22.87510471917583</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-22.87510471917583</v>
-      </c>
-      <c r="G25" t="n">
-        <v>30.344327</v>
-      </c>
-      <c r="H25" t="n">
-        <v>23.40303042242085</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>12</v>
-      </c>
-      <c r="D26" t="n">
-        <v>21.11438345650462</v>
-      </c>
-      <c r="E26" t="n">
-        <v>23.20186527469448</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-23.15468422522563</v>
-      </c>
-      <c r="G26" t="n">
-        <v>30.344327</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23.31819390288012</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SeasonalNaive</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>9</v>
-      </c>
-      <c r="D27" t="n">
-        <v>47.67483140166131</v>
-      </c>
-      <c r="E27" t="n">
-        <v>49.84978186600387</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-49.84978186600384</v>
-      </c>
-      <c r="G27" t="n">
-        <v>42.30381399999999</v>
-      </c>
-      <c r="H27" t="n">
         <v>21.215455</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>9</v>
-      </c>
-      <c r="D28" t="n">
-        <v>23.17404279245229</v>
-      </c>
-      <c r="E28" t="n">
-        <v>25.93694724882839</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-25.15318257573291</v>
-      </c>
-      <c r="G28" t="n">
-        <v>42.30381399999999</v>
-      </c>
-      <c r="H28" t="n">
-        <v>31.66305842808153</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>9</v>
-      </c>
-      <c r="D29" t="n">
-        <v>33.44483550687223</v>
-      </c>
-      <c r="E29" t="n">
-        <v>36.7514026939735</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-35.55504519697351</v>
-      </c>
-      <c r="G29" t="n">
-        <v>42.30381399999999</v>
-      </c>
-      <c r="H29" t="n">
-        <v>27.26267381225639</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>9</v>
-      </c>
-      <c r="D30" t="n">
-        <v>35.50537829448182</v>
-      </c>
-      <c r="E30" t="n">
-        <v>39.26770706222884</v>
-      </c>
-      <c r="F30" t="n">
-        <v>-38.79930033502983</v>
-      </c>
-      <c r="G30" t="n">
-        <v>42.30381399999999</v>
-      </c>
-      <c r="H30" t="n">
-        <v>25.8902301529676</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>9</v>
-      </c>
-      <c r="D31" t="n">
-        <v>36.735270924027</v>
-      </c>
-      <c r="E31" t="n">
-        <v>40.52305289490368</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-40.30075259187601</v>
-      </c>
-      <c r="G31" t="n">
-        <v>42.30381399999999</v>
-      </c>
-      <c r="H31" t="n">
-        <v>25.25505858293259</v>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -18421,129 +18000,3119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>origin</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>mean_MAPE_pct</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>mean_WAPE_pct</t>
+          <t>forecast_months</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>mean_abs_annual_total_error_pct</t>
+          <t>mape_pct</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>selected</t>
+          <t>wape_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_error_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>19.14138118648492</v>
+      <c r="A2" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>19.9887096386637</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>18.37768811666734</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
+        <v>15.59945123096836</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15.88110830194852</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-14.62288613039187</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18.73172099056072</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19.05454128669912</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-19.05454128669913</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18.34470534065316</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18.70367391440526</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-18.70367391440525</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18.8605126977973</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19.19041028193407</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-19.19041028193406</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10.79458183261901</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.0925492772236</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-11.0925492772236</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>GradientBoosting</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>20.7712248408585</v>
-      </c>
-      <c r="C3" t="n">
-        <v>21.62924831613738</v>
-      </c>
-      <c r="D3" t="n">
-        <v>20.89332249117451</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15.36474700252504</v>
+      </c>
+      <c r="E7" t="n">
+        <v>15.82449500370378</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-15.82449500370377</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>RandomForest</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>21.73226819762779</v>
-      </c>
-      <c r="C4" t="n">
-        <v>22.67705842113627</v>
-      </c>
-      <c r="D4" t="n">
-        <v>21.95220385388075</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15.55985381991654</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15.97500968830233</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-15.97500968830232</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15.63906252992702</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15.88851291473096</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-14.92509155983367</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8.068168911693482</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8.280649537001585</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-7.820823932771033</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.171909073305029</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.335875446759012</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-6.397970106189497</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.334002030525895</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7.546487558477284</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-6.935928357713486</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>22.86794188300202</v>
-      </c>
-      <c r="C5" t="n">
-        <v>23.69766382022362</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22.97419510643456</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9.915050259411878</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9.977385270188261</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-7.140452500619161</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>15.11957971685707</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15.50897854403451</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-15.50897854403452</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14.72491626103266</v>
+      </c>
+      <c r="E15" t="n">
+        <v>15.06136506293368</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-15.06136506293369</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>SeasonalNaive</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>26.02030691779865</v>
-      </c>
-      <c r="C6" t="n">
-        <v>26.30983072118109</v>
-      </c>
-      <c r="D6" t="n">
-        <v>24.81964744998939</v>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
+      <c r="C16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17.34195210257949</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.61932735124743</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-11.33887721179344</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>12.76077024919483</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12.15733707327151</v>
+      </c>
+      <c r="F17" t="n">
+        <v>12.15733707327152</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12.71508353536305</v>
+      </c>
+      <c r="E18" t="n">
+        <v>12.01905368563436</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12.01905368563434</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14.29728493339122</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13.69278636517567</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13.69278636517565</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10.3642686022197</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10.01838060295083</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.314497675163157</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10.73842537260673</v>
+      </c>
+      <c r="E21" t="n">
+        <v>11.09810037002148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-10.06484284399187</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" t="n">
+        <v>11.63902063621364</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11.93602394263841</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-11.38793332242337</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" t="n">
+        <v>17.67549831660667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>17.58233690106516</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.8203047546923803</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14.39457317618319</v>
+      </c>
+      <c r="E24" t="n">
+        <v>13.69558069371309</v>
+      </c>
+      <c r="F24" t="n">
+        <v>13.60524854015118</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13.57469508758879</v>
+      </c>
+      <c r="E25" t="n">
+        <v>12.85709977489155</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12.74249818774653</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14.70514685882168</v>
+      </c>
+      <c r="E26" t="n">
+        <v>14.00537521738446</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14.00537521738445</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>12</v>
+      </c>
+      <c r="D27" t="n">
+        <v>13.72337354707444</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12.97892470563822</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12.71458607339902</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9.409349311562787</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9.779258424498934</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-5.58471333205178</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" t="n">
+        <v>11.29732155851863</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10.60981480116542</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.13801947377661</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" t="n">
+        <v>18.65439035698309</v>
+      </c>
+      <c r="E30" t="n">
+        <v>17.97718703551643</v>
+      </c>
+      <c r="F30" t="n">
+        <v>14.39959164423285</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" t="n">
+        <v>23.1441169102926</v>
+      </c>
+      <c r="E31" t="n">
+        <v>22.36041326262715</v>
+      </c>
+      <c r="F31" t="n">
+        <v>22.36041326262713</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" t="n">
+        <v>22.48384557168044</v>
+      </c>
+      <c r="E32" t="n">
+        <v>21.60758103734666</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.60758103734666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" t="n">
+        <v>23.12536454553276</v>
+      </c>
+      <c r="E33" t="n">
+        <v>22.30160955514</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.30160955514</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>12</v>
+      </c>
+      <c r="D34" t="n">
+        <v>20.69301522011358</v>
+      </c>
+      <c r="E34" t="n">
+        <v>19.91280476061695</v>
+      </c>
+      <c r="F34" t="n">
+        <v>19.83254382698527</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.36106498342233</v>
+      </c>
+      <c r="E35" t="n">
+        <v>14.7048214820273</v>
+      </c>
+      <c r="F35" t="n">
+        <v>14.67932738906065</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" t="n">
+        <v>17.59364657605738</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.80036519556015</v>
+      </c>
+      <c r="F36" t="n">
+        <v>16.12231938941353</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>12</v>
+      </c>
+      <c r="D37" t="n">
+        <v>26.84262464392028</v>
+      </c>
+      <c r="E37" t="n">
+        <v>25.50372900861116</v>
+      </c>
+      <c r="F37" t="n">
+        <v>25.50372900861116</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19.37754456727627</v>
+      </c>
+      <c r="E38" t="n">
+        <v>17.97234589059579</v>
+      </c>
+      <c r="F38" t="n">
+        <v>17.9723458905958</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>12</v>
+      </c>
+      <c r="D39" t="n">
+        <v>20.38642091581653</v>
+      </c>
+      <c r="E39" t="n">
+        <v>18.88975385787554</v>
+      </c>
+      <c r="F39" t="n">
+        <v>18.88975385787552</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" t="n">
+        <v>20.29401785990318</v>
+      </c>
+      <c r="E40" t="n">
+        <v>18.78893160710103</v>
+      </c>
+      <c r="F40" t="n">
+        <v>18.78893160710103</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="n">
+        <v>26.93908200657201</v>
+      </c>
+      <c r="E41" t="n">
+        <v>25.35388061860511</v>
+      </c>
+      <c r="F41" t="n">
+        <v>25.3538806186051</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>12</v>
+      </c>
+      <c r="D42" t="n">
+        <v>18.72600654489068</v>
+      </c>
+      <c r="E42" t="n">
+        <v>17.67581535494176</v>
+      </c>
+      <c r="F42" t="n">
+        <v>17.67581535494176</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>12</v>
+      </c>
+      <c r="D43" t="n">
+        <v>17.63150221971675</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.87076402389526</v>
+      </c>
+      <c r="F43" t="n">
+        <v>16.87076402389526</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" t="n">
+        <v>30.25692243015505</v>
+      </c>
+      <c r="E44" t="n">
+        <v>29.50660695348247</v>
+      </c>
+      <c r="F44" t="n">
+        <v>29.50660695348248</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>12</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.15538092625813</v>
+      </c>
+      <c r="E45" t="n">
+        <v>14.99784317488634</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14.99784317488635</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>12</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.80970080526688</v>
+      </c>
+      <c r="E46" t="n">
+        <v>15.62835088723419</v>
+      </c>
+      <c r="F46" t="n">
+        <v>15.62835088723419</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>12</v>
+      </c>
+      <c r="D47" t="n">
+        <v>19.28797653418611</v>
+      </c>
+      <c r="E47" t="n">
+        <v>18.07803776198488</v>
+      </c>
+      <c r="F47" t="n">
+        <v>18.07803776198488</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>12</v>
+      </c>
+      <c r="D48" t="n">
+        <v>30.39739809010127</v>
+      </c>
+      <c r="E48" t="n">
+        <v>28.60961800664688</v>
+      </c>
+      <c r="F48" t="n">
+        <v>28.6096180066469</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>12</v>
+      </c>
+      <c r="D49" t="n">
+        <v>17.38264540126318</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.2023941779275</v>
+      </c>
+      <c r="F49" t="n">
+        <v>16.11922739447719</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15.35023917497219</v>
+      </c>
+      <c r="E50" t="n">
+        <v>14.12384814894695</v>
+      </c>
+      <c r="F50" t="n">
+        <v>13.77849610805538</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>12</v>
+      </c>
+      <c r="D51" t="n">
+        <v>26.09335617369332</v>
+      </c>
+      <c r="E51" t="n">
+        <v>25.05416966744004</v>
+      </c>
+      <c r="F51" t="n">
+        <v>24.94090047167105</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>12</v>
+      </c>
+      <c r="D52" t="n">
+        <v>17.45594565705953</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.5881283458942</v>
+      </c>
+      <c r="F52" t="n">
+        <v>16.58812834589418</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>12</v>
+      </c>
+      <c r="D53" t="n">
+        <v>17.15305497647231</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.29112267575564</v>
+      </c>
+      <c r="F53" t="n">
+        <v>16.29112267575564</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>12</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.59416942961249</v>
+      </c>
+      <c r="E54" t="n">
+        <v>15.74030820015916</v>
+      </c>
+      <c r="F54" t="n">
+        <v>15.74030820015915</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>12</v>
+      </c>
+      <c r="D55" t="n">
+        <v>34.96794190698704</v>
+      </c>
+      <c r="E55" t="n">
+        <v>34.01982425587369</v>
+      </c>
+      <c r="F55" t="n">
+        <v>34.0198242558737</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>12</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.88539447081103</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.01078944509739</v>
+      </c>
+      <c r="F56" t="n">
+        <v>15.81814419273201</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>12</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.2732494475509</v>
+      </c>
+      <c r="E57" t="n">
+        <v>15.38277413362202</v>
+      </c>
+      <c r="F57" t="n">
+        <v>15.382774133622</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>12</v>
+      </c>
+      <c r="D58" t="n">
+        <v>20.4450576597624</v>
+      </c>
+      <c r="E58" t="n">
+        <v>18.93917038837919</v>
+      </c>
+      <c r="F58" t="n">
+        <v>15.43606747188892</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>12</v>
+      </c>
+      <c r="D59" t="n">
+        <v>10.54228352922363</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.18122136235959</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.390138903901873</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" t="n">
+        <v>10.40128762984633</v>
+      </c>
+      <c r="E60" t="n">
+        <v>10.03101998079455</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.525909643410142</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>12</v>
+      </c>
+      <c r="D61" t="n">
+        <v>10.5711462862181</v>
+      </c>
+      <c r="E61" t="n">
+        <v>10.12582136170896</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.507995351206322</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>12</v>
+      </c>
+      <c r="D62" t="n">
+        <v>29.39430123209818</v>
+      </c>
+      <c r="E62" t="n">
+        <v>28.9333455645774</v>
+      </c>
+      <c r="F62" t="n">
+        <v>28.93334556457743</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>12</v>
+      </c>
+      <c r="D63" t="n">
+        <v>14.50438792244816</v>
+      </c>
+      <c r="E63" t="n">
+        <v>13.58558908335442</v>
+      </c>
+      <c r="F63" t="n">
+        <v>12.46081957328408</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>12</v>
+      </c>
+      <c r="D64" t="n">
+        <v>14.97286945976345</v>
+      </c>
+      <c r="E64" t="n">
+        <v>14.02072720535332</v>
+      </c>
+      <c r="F64" t="n">
+        <v>13.01593097578237</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>12</v>
+      </c>
+      <c r="D65" t="n">
+        <v>15.55739982890275</v>
+      </c>
+      <c r="E65" t="n">
+        <v>15.36762253240286</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.897426993231454</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>12</v>
+      </c>
+      <c r="D66" t="n">
+        <v>10.23180341453217</v>
+      </c>
+      <c r="E66" t="n">
+        <v>10.80890918190472</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-8.074928157346488</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>12</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10.34596792008585</v>
+      </c>
+      <c r="E67" t="n">
+        <v>10.94947264447045</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-8.582477275515698</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>12</v>
+      </c>
+      <c r="D68" t="n">
+        <v>9.838350114958612</v>
+      </c>
+      <c r="E68" t="n">
+        <v>10.42417844702736</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-7.964245442041705</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>12</v>
+      </c>
+      <c r="D69" t="n">
+        <v>16.02768385705198</v>
+      </c>
+      <c r="E69" t="n">
+        <v>15.11952283854143</v>
+      </c>
+      <c r="F69" t="n">
+        <v>15.11952283854143</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>12</v>
+      </c>
+      <c r="D70" t="n">
+        <v>7.299612232431055</v>
+      </c>
+      <c r="E70" t="n">
+        <v>6.90337584387512</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.900797207643206</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>12</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7.508885965480598</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7.289503660894954</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.9946758757302033</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>12</v>
+      </c>
+      <c r="D72" t="n">
+        <v>17.17239009960314</v>
+      </c>
+      <c r="E72" t="n">
+        <v>18.65415183208813</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-14.21626844141857</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>12</v>
+      </c>
+      <c r="D73" t="n">
+        <v>18.77793240473453</v>
+      </c>
+      <c r="E73" t="n">
+        <v>20.26996815935917</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-20.26996815935917</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>12</v>
+      </c>
+      <c r="D74" t="n">
+        <v>18.19330488590125</v>
+      </c>
+      <c r="E74" t="n">
+        <v>19.69352823135158</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-19.6935282313516</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>12</v>
+      </c>
+      <c r="D75" t="n">
+        <v>17.6827468434885</v>
+      </c>
+      <c r="E75" t="n">
+        <v>19.23102482879862</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-19.23102482879862</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>12</v>
+      </c>
+      <c r="D76" t="n">
+        <v>9.966050931712047</v>
+      </c>
+      <c r="E76" t="n">
+        <v>10.36020687488296</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-6.412798720299885</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>12</v>
+      </c>
+      <c r="D77" t="n">
+        <v>14.52700263853233</v>
+      </c>
+      <c r="E77" t="n">
+        <v>15.31975204275683</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-13.52217783102797</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" t="n">
+        <v>13.84056213004615</v>
+      </c>
+      <c r="E78" t="n">
+        <v>14.76685361263065</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-12.68112798825186</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>12</v>
+      </c>
+      <c r="D79" t="n">
+        <v>24.1781595512505</v>
+      </c>
+      <c r="E79" t="n">
+        <v>26.36648803917413</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-25.7104060337405</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>12</v>
+      </c>
+      <c r="D80" t="n">
+        <v>15.64357758272476</v>
+      </c>
+      <c r="E80" t="n">
+        <v>17.74744057197239</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-16.68969088475079</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>12</v>
+      </c>
+      <c r="D81" t="n">
+        <v>15.91201893549144</v>
+      </c>
+      <c r="E81" t="n">
+        <v>17.99059203331939</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-16.7741140211746</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>12</v>
+      </c>
+      <c r="D82" t="n">
+        <v>16.3876280977711</v>
+      </c>
+      <c r="E82" t="n">
+        <v>18.58788934809515</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-17.87546340937452</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>12</v>
+      </c>
+      <c r="D83" t="n">
+        <v>13.49812675148102</v>
+      </c>
+      <c r="E83" t="n">
+        <v>14.08892734639234</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-9.281531485410349</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>12</v>
+      </c>
+      <c r="D84" t="n">
+        <v>16.26503118460117</v>
+      </c>
+      <c r="E84" t="n">
+        <v>17.60138353015452</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-13.37217913894855</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>12</v>
+      </c>
+      <c r="D85" t="n">
+        <v>17.37175740317237</v>
+      </c>
+      <c r="E85" t="n">
+        <v>19.08151895899972</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-15.92494568980217</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>12</v>
+      </c>
+      <c r="D86" t="n">
+        <v>30.15069438637898</v>
+      </c>
+      <c r="E86" t="n">
+        <v>31.23982264401483</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-30.63764349619516</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>12</v>
+      </c>
+      <c r="D87" t="n">
+        <v>22.58208190006742</v>
+      </c>
+      <c r="E87" t="n">
+        <v>24.13234010088585</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-23.39484936186131</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>12</v>
+      </c>
+      <c r="D88" t="n">
+        <v>22.718659662082</v>
+      </c>
+      <c r="E88" t="n">
+        <v>24.20474832923641</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-23.27878541238041</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>12</v>
+      </c>
+      <c r="D89" t="n">
+        <v>22.39297110914359</v>
+      </c>
+      <c r="E89" t="n">
+        <v>23.92262343819577</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-23.15255626138471</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>12</v>
+      </c>
+      <c r="D90" t="n">
+        <v>20.02541955152969</v>
+      </c>
+      <c r="E90" t="n">
+        <v>20.36450344722937</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-17.30030959512665</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>12</v>
+      </c>
+      <c r="D91" t="n">
+        <v>22.68586044686468</v>
+      </c>
+      <c r="E91" t="n">
+        <v>23.51777254633411</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-20.72088792679291</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>12</v>
+      </c>
+      <c r="D92" t="n">
+        <v>24.41758494949779</v>
+      </c>
+      <c r="E92" t="n">
+        <v>25.54133026800367</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-23.14452625268463</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>12</v>
+      </c>
+      <c r="D93" t="n">
+        <v>32.87320485142487</v>
+      </c>
+      <c r="E93" t="n">
+        <v>32.88472837438296</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-32.88472837438296</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>12</v>
+      </c>
+      <c r="D94" t="n">
+        <v>22.25872924161968</v>
+      </c>
+      <c r="E94" t="n">
+        <v>22.60744691806349</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-22.60744691806348</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>12</v>
+      </c>
+      <c r="D95" t="n">
+        <v>21.71119438019672</v>
+      </c>
+      <c r="E95" t="n">
+        <v>22.05214312031276</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-22.05214312031276</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>12</v>
+      </c>
+      <c r="D96" t="n">
+        <v>22.93171085718082</v>
+      </c>
+      <c r="E96" t="n">
+        <v>23.25927485053198</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-23.25927485053199</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>12</v>
+      </c>
+      <c r="D97" t="n">
+        <v>23.50225538730532</v>
+      </c>
+      <c r="E97" t="n">
+        <v>23.7637698624352</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-23.7637698624352</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>12</v>
+      </c>
+      <c r="D98" t="n">
+        <v>17.84902146426296</v>
+      </c>
+      <c r="E98" t="n">
+        <v>18.19984963212151</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-18.1998496321215</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>12</v>
+      </c>
+      <c r="D99" t="n">
+        <v>29.87863359013381</v>
+      </c>
+      <c r="E99" t="n">
+        <v>30.27977609791026</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-30.27977609791026</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>12</v>
+      </c>
+      <c r="D100" t="n">
+        <v>28.24277945900172</v>
+      </c>
+      <c r="E100" t="n">
+        <v>28.19262563595733</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-28.19262563595732</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>12</v>
+      </c>
+      <c r="D101" t="n">
+        <v>9.188929370970307</v>
+      </c>
+      <c r="E101" t="n">
+        <v>9.366648806689742</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-9.366648806689737</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>12</v>
+      </c>
+      <c r="D102" t="n">
+        <v>8.878908400402096</v>
+      </c>
+      <c r="E102" t="n">
+        <v>9.079804464315989</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-9.079804464315982</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>12</v>
+      </c>
+      <c r="D103" t="n">
+        <v>7.94113293705947</v>
+      </c>
+      <c r="E103" t="n">
+        <v>8.135838274963081</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-8.135838274963078</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>12</v>
+      </c>
+      <c r="D104" t="n">
+        <v>14.53338447573811</v>
+      </c>
+      <c r="E104" t="n">
+        <v>14.71509110737211</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-14.71509110737209</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>12</v>
+      </c>
+      <c r="D105" t="n">
+        <v>18.64661837808467</v>
+      </c>
+      <c r="E105" t="n">
+        <v>18.85098767611636</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-18.85098767611634</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>12</v>
+      </c>
+      <c r="D106" t="n">
+        <v>27.78963207393304</v>
+      </c>
+      <c r="E106" t="n">
+        <v>27.98073452290593</v>
+      </c>
+      <c r="F106" t="n">
+        <v>-27.98073452290592</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>12</v>
+      </c>
+      <c r="D107" t="n">
+        <v>23.43680819717718</v>
+      </c>
+      <c r="E107" t="n">
+        <v>23.07203362121206</v>
+      </c>
+      <c r="F107" t="n">
+        <v>-23.07203362121205</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>12</v>
+      </c>
+      <c r="D108" t="n">
+        <v>8.263302077822377</v>
+      </c>
+      <c r="E108" t="n">
+        <v>8.476192387101914</v>
+      </c>
+      <c r="F108" t="n">
+        <v>-1.888729849781414</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>12</v>
+      </c>
+      <c r="D109" t="n">
+        <v>8.136318372144762</v>
+      </c>
+      <c r="E109" t="n">
+        <v>8.298212122825205</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-0.381587445874631</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>12</v>
+      </c>
+      <c r="D110" t="n">
+        <v>8.367817869770082</v>
+      </c>
+      <c r="E110" t="n">
+        <v>8.548065576978054</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-1.526743771495785</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>12</v>
+      </c>
+      <c r="D111" t="n">
+        <v>13.39292844144565</v>
+      </c>
+      <c r="E111" t="n">
+        <v>14.5491660325723</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-13.96335556343801</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>12</v>
+      </c>
+      <c r="D112" t="n">
+        <v>16.20599822118782</v>
+      </c>
+      <c r="E112" t="n">
+        <v>17.36689426951666</v>
+      </c>
+      <c r="F112" t="n">
+        <v>-17.36689426951665</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>12</v>
+      </c>
+      <c r="D113" t="n">
+        <v>17.66948752040499</v>
+      </c>
+      <c r="E113" t="n">
+        <v>18.84747068271408</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-18.84747068271407</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" t="n">
+        <v>23.59741647103776</v>
+      </c>
+      <c r="E114" t="n">
+        <v>23.97191409122371</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-23.97191409122371</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>12</v>
+      </c>
+      <c r="D115" t="n">
+        <v>16.67404099631285</v>
+      </c>
+      <c r="E115" t="n">
+        <v>18.26679457058207</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-17.91300330918168</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>12</v>
+      </c>
+      <c r="D116" t="n">
+        <v>16.78642368321008</v>
+      </c>
+      <c r="E116" t="n">
+        <v>18.46791036834922</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-18.32289790265684</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>12</v>
+      </c>
+      <c r="D117" t="n">
+        <v>15.6477350323475</v>
+      </c>
+      <c r="E117" t="n">
+        <v>17.1223291729367</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-16.06873177639595</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>12</v>
+      </c>
+      <c r="D118" t="n">
+        <v>22.85549795477947</v>
+      </c>
+      <c r="E118" t="n">
+        <v>25.1313771777209</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-25.13137717772089</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>12</v>
+      </c>
+      <c r="D119" t="n">
+        <v>21.20591039540898</v>
+      </c>
+      <c r="E119" t="n">
+        <v>22.87510471917583</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-22.87510471917583</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>12</v>
+      </c>
+      <c r="D120" t="n">
+        <v>21.11438345650461</v>
+      </c>
+      <c r="E120" t="n">
+        <v>23.20186527469448</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-23.15468422522562</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>12</v>
+      </c>
+      <c r="D121" t="n">
+        <v>24.85720954393342</v>
+      </c>
+      <c r="E121" t="n">
+        <v>26.52167546791337</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-26.52167546791336</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>12</v>
+      </c>
+      <c r="D122" t="n">
+        <v>21.14777597806859</v>
+      </c>
+      <c r="E122" t="n">
+        <v>23.00092688465767</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-21.97570246620015</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>12</v>
+      </c>
+      <c r="D123" t="n">
+        <v>21.53159837658862</v>
+      </c>
+      <c r="E123" t="n">
+        <v>23.41152227853149</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-22.67101556639608</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>12</v>
+      </c>
+      <c r="D124" t="n">
+        <v>21.14206794035103</v>
+      </c>
+      <c r="E124" t="n">
+        <v>22.92266031188611</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-21.97990730565612</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>12</v>
+      </c>
+      <c r="D125" t="n">
+        <v>30.08044350290421</v>
+      </c>
+      <c r="E125" t="n">
+        <v>32.74146572100291</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-32.26158267271945</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>12</v>
+      </c>
+      <c r="D126" t="n">
+        <v>26.73958346148079</v>
+      </c>
+      <c r="E126" t="n">
+        <v>28.81428273860416</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-28.81428273860415</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>12</v>
+      </c>
+      <c r="D127" t="n">
+        <v>28.01268077551272</v>
+      </c>
+      <c r="E127" t="n">
+        <v>30.11402995925795</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-30.11402995925795</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>12</v>
+      </c>
+      <c r="D128" t="n">
+        <v>34.08292619422533</v>
+      </c>
+      <c r="E128" t="n">
+        <v>37.21700079364816</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-37.21700079364816</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>12</v>
+      </c>
+      <c r="D129" t="n">
+        <v>29.26807307157447</v>
+      </c>
+      <c r="E129" t="n">
+        <v>32.61267908411891</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-32.61267908411892</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>12</v>
+      </c>
+      <c r="D130" t="n">
+        <v>28.95987883042469</v>
+      </c>
+      <c r="E130" t="n">
+        <v>32.36166956282439</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-32.3616695628244</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>12</v>
+      </c>
+      <c r="D131" t="n">
+        <v>28.20572266432475</v>
+      </c>
+      <c r="E131" t="n">
+        <v>31.53761541823632</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-31.53761541823634</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>12</v>
+      </c>
+      <c r="D132" t="n">
+        <v>40.23827635217258</v>
+      </c>
+      <c r="E132" t="n">
+        <v>43.82546867263007</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-43.82546867263007</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>12</v>
+      </c>
+      <c r="D133" t="n">
+        <v>35.39059821445771</v>
+      </c>
+      <c r="E133" t="n">
+        <v>38.60768014279907</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-38.60768014279907</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>12</v>
+      </c>
+      <c r="D134" t="n">
+        <v>37.84865937952615</v>
+      </c>
+      <c r="E134" t="n">
+        <v>40.9460224476225</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-40.9460224476225</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>12</v>
+      </c>
+      <c r="D135" t="n">
+        <v>43.42273521552193</v>
+      </c>
+      <c r="E135" t="n">
+        <v>46.48251502945033</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-46.48251502945035</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>12</v>
+      </c>
+      <c r="D136" t="n">
+        <v>32.37653085033128</v>
+      </c>
+      <c r="E136" t="n">
+        <v>36.84838652096293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>-36.84838652096295</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>12</v>
+      </c>
+      <c r="D137" t="n">
+        <v>30.35235213528782</v>
+      </c>
+      <c r="E137" t="n">
+        <v>35.27045845757803</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-35.27045845757803</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>12</v>
+      </c>
+      <c r="D138" t="n">
+        <v>31.21308356875387</v>
+      </c>
+      <c r="E138" t="n">
+        <v>35.7145658352397</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-35.7145658352397</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>12</v>
+      </c>
+      <c r="D139" t="n">
+        <v>41.33635490400964</v>
+      </c>
+      <c r="E139" t="n">
+        <v>45.98969131015483</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-45.98969131015483</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>12</v>
+      </c>
+      <c r="D140" t="n">
+        <v>36.33480213121796</v>
+      </c>
+      <c r="E140" t="n">
+        <v>41.11431164202972</v>
+      </c>
+      <c r="F140" t="n">
+        <v>-41.11431164202973</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>12</v>
+      </c>
+      <c r="D141" t="n">
+        <v>37.1588436045938</v>
+      </c>
+      <c r="E141" t="n">
+        <v>41.93246328819975</v>
+      </c>
+      <c r="F141" t="n">
+        <v>-41.93246328819976</v>
       </c>
     </row>
   </sheetData>
@@ -18557,805 +21126,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>mean_MAPE_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mean_WAPE_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_WAPE_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>p75_WAPE_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean_abs_annual_total_error_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>folds</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>17.12836642589039</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.75717964369058</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.2292512008343</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.71872155808818</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16.66371977279894</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>17.3410294105569</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17.94379167059772</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18.33296355504002</v>
+      </c>
+      <c r="E3" t="n">
+        <v>22.45687224432653</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16.93436749359588</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>17.35216409032504</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17.97128969066736</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17.85989323128409</v>
+      </c>
+      <c r="E4" t="n">
+        <v>22.42217167648623</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16.92944269645572</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>18.33208197474586</v>
+      </c>
+      <c r="C5" t="n">
+        <v>18.97808183345455</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16.78464422372208</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19.85701693688123</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18.00407582765268</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>19.88268650012741</v>
+      </c>
+      <c r="C6" t="n">
+        <v>20.53811304881257</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.8355646097277</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26.15118133172923</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19.68665346042547</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>21.63227174036634</v>
+      </c>
+      <c r="C7" t="n">
+        <v>22.07729517266277</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20.13865410392316</v>
+      </c>
+      <c r="E7" t="n">
+        <v>28.69054989612951</v>
+      </c>
+      <c r="F7" t="n">
+        <v>20.83878984024711</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>SeasonalNaive</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>selected_model</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>selected_revenue_bn_twd</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2.853997</v>
-      </c>
-      <c r="C2" t="n">
-        <v>6.052500032374423</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6.290609086890151</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5.548570093446362</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.093671156752531</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>6.052500032374423</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="B3" t="n">
-        <v>3.024742</v>
-      </c>
-      <c r="C3" t="n">
-        <v>6.629201693365356</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6.599018783679234</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5.563564565416368</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5.028165055193742</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>6.629201693365356</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3.250133</v>
-      </c>
-      <c r="C4" t="n">
-        <v>6.720273834761776</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6.824286696633062</v>
-      </c>
-      <c r="E4" t="n">
-        <v>5.463937281875898</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4.975056743181541</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>6.720273834761776</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46388</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3.533279</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7.059251952419165</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7.145812928914194</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5.463937281875898</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4.938216972399275</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>7.059251952419165</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46419</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2.740833</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6.115390394460877</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.981289061826174</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5.473694825647678</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.808306143489652</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>6.115390394460877</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46447</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3.781706</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7.689777499179326</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8.077423372750925</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5.5154917516369</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4.873396540974471</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7.689777499179326</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46478</v>
-      </c>
       <c r="B8" t="n">
-        <v>4.610166</v>
+        <v>24.30600196215266</v>
       </c>
       <c r="C8" t="n">
-        <v>8.363532638792726</v>
+        <v>24.69613632919446</v>
       </c>
       <c r="D8" t="n">
-        <v>8.860307125554314</v>
+        <v>24.51304187933187</v>
       </c>
       <c r="E8" t="n">
-        <v>5.388751033963683</v>
+        <v>28.52112096533862</v>
       </c>
       <c r="F8" t="n">
-        <v>4.79870216254639</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>8.363532638792726</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46508</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4.794425</v>
-      </c>
-      <c r="C9" t="n">
-        <v>8.476083608684501</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9.186958306433686</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.881733088671654</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.674404653988765</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>8.476083608684501</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46539</v>
-      </c>
-      <c r="B10" t="n">
-        <v>4.895221</v>
-      </c>
-      <c r="C10" t="n">
-        <v>8.443509869966764</v>
-      </c>
-      <c r="D10" t="n">
-        <v>9.654184692265877</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.863278951951753</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4.630230820655189</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>8.443509869966764</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46569</v>
-      </c>
-      <c r="B11" t="n">
-        <v>5.908074</v>
-      </c>
-      <c r="C11" t="n">
-        <v>9.588906561170344</v>
-      </c>
-      <c r="D11" t="n">
-        <v>10.59845280609455</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4.873194763539323</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4.630118344382896</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>9.588906561170344</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46600</v>
-      </c>
-      <c r="B12" t="n">
-        <v>5.91454</v>
-      </c>
-      <c r="C12" t="n">
-        <v>9.578243519804312</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10.78254601970846</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4.848732033505578</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4.62801303414053</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>9.578243519804312</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46631</v>
-      </c>
-      <c r="B13" t="n">
-        <v>6.12557</v>
-      </c>
-      <c r="C13" t="n">
-        <v>9.722303470573241</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11.2509097787464</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4.853913974454581</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4.618826851971575</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>9.722303470573241</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46661</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2.853997</v>
-      </c>
-      <c r="C14" t="n">
-        <v>9.406356012306983</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.60028521865141</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4.80760652811697</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4.611412222968108</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>9.406356012306983</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46692</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3.024742</v>
-      </c>
-      <c r="C15" t="n">
-        <v>10.11864448149777</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.0841948179077</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4.786204355925846</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4.619585218610831</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>10.11864448149777</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46722</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3.250133</v>
-      </c>
-      <c r="C16" t="n">
-        <v>10.0881315534913</v>
-      </c>
-      <c r="D16" t="n">
-        <v>12.65054425562481</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4.772086312302483</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4.61711664538098</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>10.0881315534913</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46753</v>
-      </c>
-      <c r="B17" t="n">
-        <v>3.533279</v>
-      </c>
-      <c r="C17" t="n">
-        <v>10.43442574494529</v>
-      </c>
-      <c r="D17" t="n">
-        <v>13.42407673500937</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4.65733190234309</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4.603065792775702</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>10.43442574494529</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46784</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2.740833</v>
-      </c>
-      <c r="C18" t="n">
-        <v>8.910214294751977</v>
-      </c>
-      <c r="D18" t="n">
-        <v>13.6505318288008</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4.649668588280484</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4.597012280339975</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>8.910214294751977</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46813</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3.781706</v>
-      </c>
-      <c r="C19" t="n">
-        <v>11.05482879487644</v>
-      </c>
-      <c r="D19" t="n">
-        <v>15.32409632984484</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4.656975700011996</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4.601779874221593</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>11.05482879487644</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46844</v>
-      </c>
-      <c r="B20" t="n">
-        <v>4.610166</v>
-      </c>
-      <c r="C20" t="n">
-        <v>11.87356267807803</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.99031825904354</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4.771721333317892</v>
-      </c>
-      <c r="F20" t="n">
-        <v>4.61093215240409</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>11.87356267807803</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46874</v>
-      </c>
-      <c r="B21" t="n">
-        <v>4.794425</v>
-      </c>
-      <c r="C21" t="n">
-        <v>11.89274834749709</v>
-      </c>
-      <c r="D21" t="n">
-        <v>18.39197095410458</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4.779585807635184</v>
-      </c>
-      <c r="F21" t="n">
-        <v>4.61093215240409</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>11.89274834749709</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46905</v>
-      </c>
-      <c r="B22" t="n">
-        <v>4.895221</v>
-      </c>
-      <c r="C22" t="n">
-        <v>11.71700901302331</v>
-      </c>
-      <c r="D22" t="n">
-        <v>20.00112324190608</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4.831441800600816</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4.625007017062347</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>11.71700901302331</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46935</v>
-      </c>
-      <c r="B23" t="n">
-        <v>5.908074</v>
-      </c>
-      <c r="C23" t="n">
-        <v>13.16900099043921</v>
-      </c>
-      <c r="D23" t="n">
-        <v>22.26678372492472</v>
-      </c>
-      <c r="E23" t="n">
-        <v>4.845735445275425</v>
-      </c>
-      <c r="F23" t="n">
-        <v>4.630118344382899</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>13.16900099043921</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46966</v>
-      </c>
-      <c r="B24" t="n">
-        <v>5.91454</v>
-      </c>
-      <c r="C24" t="n">
-        <v>13.02621673736187</v>
-      </c>
-      <c r="D24" t="n">
-        <v>23.86063069267166</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4.873194763539323</v>
-      </c>
-      <c r="F24" t="n">
-        <v>4.62801303414053</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>13.02621673736187</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46997</v>
-      </c>
-      <c r="B25" t="n">
-        <v>6.12557</v>
-      </c>
-      <c r="C25" t="n">
-        <v>13.10047951740674</v>
-      </c>
-      <c r="D25" t="n">
-        <v>25.73930445370227</v>
-      </c>
-      <c r="E25" t="n">
-        <v>4.878402848317601</v>
-      </c>
-      <c r="F25" t="n">
-        <v>4.61882685197158</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>13.10047951740674</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>47027</v>
-      </c>
-      <c r="B26" t="n">
-        <v>2.853997</v>
-      </c>
-      <c r="C26" t="n">
-        <v>12.56442329411764</v>
-      </c>
-      <c r="D26" t="n">
-        <v>27.62672594480376</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4.831861772538214</v>
-      </c>
-      <c r="F26" t="n">
-        <v>4.611412222968113</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>12.56442329411764</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>47058</v>
-      </c>
-      <c r="B27" t="n">
-        <v>3.024742</v>
-      </c>
-      <c r="C27" t="n">
-        <v>13.40438339422614</v>
-      </c>
-      <c r="D27" t="n">
-        <v>29.83752145644316</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4.804635356058417</v>
-      </c>
-      <c r="F27" t="n">
-        <v>4.619585218610831</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>13.40438339422614</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>47088</v>
-      </c>
-      <c r="B28" t="n">
-        <v>3.250133</v>
-      </c>
-      <c r="C28" t="n">
-        <v>13.25938319188964</v>
-      </c>
-      <c r="D28" t="n">
-        <v>32.40706463973146</v>
-      </c>
-      <c r="E28" t="n">
-        <v>4.790462945833768</v>
-      </c>
-      <c r="F28" t="n">
-        <v>4.617116645380979</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>HW_Damped</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>13.25938319188964</v>
+        <v>22.11491465924857</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19369,6 +21378,990 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SeasonalNaive</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>HW_Damped_Mul</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>HW_Log_Damped_Add</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>selected_model</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>selected_revenue_bn_twd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2.853997</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6.052500032374423</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.409284427069665</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.043551834588982</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6.290609086890151</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.548570093446362</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.09367115675253</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>6.409284427069665</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3.024742</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6.629201693365356</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.801619701369838</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.630824362264261</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.599018783679234</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.563564565416368</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.028165055193742</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>6.801619701369838</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3.250133</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6.720273834761776</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.073491492540579</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.750750878071914</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.824286696633062</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.463937281875898</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.975056743181538</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>7.073491492540579</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.533279</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.059251952419165</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.396971359104222</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.102013674313353</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7.145812928914194</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.463937281875898</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.938216972399274</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>7.396971359104222</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2.740833</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6.115390394460877</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.478456877832667</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.353233149762191</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.981289061826174</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.473694825647678</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.808306143489649</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>7.478456877832667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.781706</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7.689777499179326</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8.073439150371287</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8.050565320943493</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.077423372750925</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.5154917516369</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.87339654097447</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>8.073439150371287</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4.610166</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8.363532638792726</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.420897387940881</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8.433912266944946</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8.860307125554314</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.388751033963683</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.798702162546392</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>8.420897387940881</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46508</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4.794425</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.476083608684501</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.697942759316359</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8.66750917605655</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.186958306433686</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.881733088671654</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.674404653988762</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>8.697942759316359</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46539</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4.895221</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8.443509869966764</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8.930592335364237</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8.559978570018929</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.654184692265877</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.863278951951753</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.630230820655189</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>8.930592335364237</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46569</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5.908074</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.588906561170344</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.372086892263848</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.570162506486829</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10.59845280609455</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.873194763539323</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.630118344382897</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>9.372086892263848</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46600</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5.91454</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9.578243519804312</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9.654430086395138</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.01530663234112</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10.78254601970846</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.848732033505578</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.62801303414053</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>9.654430086395138</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46631</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6.12557</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9.722303470573241</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9.920769578839003</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10.16642993481031</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11.2509097787464</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.853913974454581</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.618826851971574</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>9.920769578839003</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46661</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2.853997</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9.406356012306983</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10.138313407874</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10.03755889542047</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11.60028521865141</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.80760652811697</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.611412222968113</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>10.138313407874</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46692</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.024742</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10.11864448149777</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10.51200353727015</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.98504145913701</v>
+      </c>
+      <c r="F15" t="n">
+        <v>12.0841948179077</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.786204355925846</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.619585218610833</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>10.51200353727015</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46722</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.250133</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10.0881315534913</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10.76532340926139</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.15552686981486</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12.65054425562481</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.772086312302483</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.617116645380977</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>10.76532340926139</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46753</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.533279</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10.43442574494529</v>
+      </c>
+      <c r="D17" t="n">
+        <v>11.07034411624143</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.70654716372978</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13.42407673500937</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.65733190234309</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.6030657927757</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>11.07034411624143</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46784</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2.740833</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8.910214294751977</v>
+      </c>
+      <c r="D18" t="n">
+        <v>11.13346277118419</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.44616476811997</v>
+      </c>
+      <c r="F18" t="n">
+        <v>13.6505318288008</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.649668588280484</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.597012280339974</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>11.13346277118419</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46813</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3.781706</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11.05482879487644</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11.71017001425605</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13.20409517882199</v>
+      </c>
+      <c r="F19" t="n">
+        <v>15.32409632984484</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.656975700011996</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.601779874221593</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>11.71017001425605</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46844</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4.610166</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11.87356267807803</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12.03944459750622</v>
+      </c>
+      <c r="E20" t="n">
+        <v>13.79866069762164</v>
+      </c>
+      <c r="F20" t="n">
+        <v>16.99031825904354</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.771721333317892</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.61093215240409</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>12.03944459750622</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46874</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4.794425</v>
+      </c>
+      <c r="C21" t="n">
+        <v>11.89274834749709</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12.29839723283387</v>
+      </c>
+      <c r="E21" t="n">
+        <v>14.14598285946612</v>
+      </c>
+      <c r="F21" t="n">
+        <v>18.39197095410458</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.779585807635184</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.610932152404088</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>12.29839723283387</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4.895221</v>
+      </c>
+      <c r="C22" t="n">
+        <v>11.71700901302331</v>
+      </c>
+      <c r="D22" t="n">
+        <v>12.51304453651416</v>
+      </c>
+      <c r="E22" t="n">
+        <v>13.93631008034823</v>
+      </c>
+      <c r="F22" t="n">
+        <v>20.00112324190608</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.831441800600816</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.625007017062345</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>12.51304453651416</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46935</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5.908074</v>
+      </c>
+      <c r="C23" t="n">
+        <v>13.16900099043921</v>
+      </c>
+      <c r="D23" t="n">
+        <v>12.93662683240802</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.54304341559182</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22.26678372492472</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.845735445275425</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.630118344382896</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>12.93662683240802</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46966</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5.91454</v>
+      </c>
+      <c r="C24" t="n">
+        <v>13.02621673736187</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13.20114732683859</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.2266143389462</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.86063069267166</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.873194763539323</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.628013034140532</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>13.20114732683859</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46997</v>
+      </c>
+      <c r="B25" t="n">
+        <v>6.12557</v>
+      </c>
+      <c r="C25" t="n">
+        <v>13.10047951740674</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13.44975323308024</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.43176887297117</v>
+      </c>
+      <c r="F25" t="n">
+        <v>25.73930445370227</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.878402848317601</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.618826851971578</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>13.44975323308024</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>47027</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2.853997</v>
+      </c>
+      <c r="C26" t="n">
+        <v>12.56442329411764</v>
+      </c>
+      <c r="D26" t="n">
+        <v>13.64965214384403</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.18457773682623</v>
+      </c>
+      <c r="F26" t="n">
+        <v>27.62672594480376</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.831861772538214</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.611412222968113</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>13.64965214384403</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>47058</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.024742</v>
+      </c>
+      <c r="C27" t="n">
+        <v>13.40438339422614</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14.00578557956033</v>
+      </c>
+      <c r="E27" t="n">
+        <v>17.67004275902729</v>
+      </c>
+      <c r="F27" t="n">
+        <v>29.83752145644316</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.804635356058417</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.619585218610832</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>14.00578557956033</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>47088</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.250133</v>
+      </c>
+      <c r="C28" t="n">
+        <v>13.25938319188964</v>
+      </c>
+      <c r="D28" t="n">
+        <v>14.24163654134012</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.90168072270541</v>
+      </c>
+      <c r="F28" t="n">
+        <v>32.40706463973146</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4.790462945833768</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.61711664538098</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>HW_Damped_Add</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>14.24163654134012</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -19399,14 +22392,14 @@
         <v>2026</v>
       </c>
       <c r="B2" t="n">
-        <v>61.70578956050154</v>
+        <v>62.58820962098007</v>
       </c>
       <c r="C2" t="n">
-        <v>103.3519793024296</v>
+        <v>106.2600024742024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HW_Damped</t>
+          <t>HW_Damped_Add</t>
         </is>
       </c>
     </row>
@@ -19415,14 +22408,14 @@
         <v>2027</v>
       </c>
       <c r="B3" t="n">
-        <v>104.6501315623473</v>
+        <v>109.3612267818332</v>
       </c>
       <c r="C3" t="n">
-        <v>69.59532048405204</v>
+        <v>74.73135506527484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HW_Damped</t>
+          <t>HW_Damped_Add</t>
         </is>
       </c>
     </row>
@@ -19431,14 +22424,14 @@
         <v>2028</v>
       </c>
       <c r="B4" t="n">
-        <v>144.4066759986134</v>
+        <v>152.2494649256073</v>
       </c>
       <c r="C4" t="n">
-        <v>37.98996125731611</v>
+        <v>39.21704191315689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HW_Damped</t>
+          <t>HW_Damped_Add</t>
         </is>
       </c>
     </row>
